--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbPrdBaseinfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbPrdBaseinfo.xlsx
@@ -1,102 +1,130 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\dev0401-huaxia\tams\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView windowWidth="19815" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
     <sheet name="CHB_PRD_BASEINFO_ENUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
+  <si>
+    <t>操作类型</t>
+  </si>
+  <si>
+    <t>产品代码</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>募集起始日期</t>
+  </si>
+  <si>
+    <t>募集结束日期</t>
+  </si>
+  <si>
+    <t>起息日</t>
+  </si>
+  <si>
+    <t>到期日</t>
+  </si>
+  <si>
+    <t>管理方式</t>
+  </si>
+  <si>
+    <t>是否结构化分级产品</t>
+  </si>
+  <si>
+    <t>业绩比较基准上限%</t>
+  </si>
+  <si>
+    <t>业绩比较基准下限%</t>
+  </si>
+  <si>
+    <t>业绩比较基准说明</t>
+  </si>
+  <si>
+    <t>开放模式</t>
+  </si>
+  <si>
+    <t>规律开放周期</t>
+  </si>
+  <si>
+    <t>其他规律开放周期（天）</t>
+  </si>
+  <si>
+    <t>无规律开放说明</t>
+  </si>
+  <si>
+    <t>首次开放周期起始日</t>
+  </si>
+  <si>
+    <t>节假日是否开放</t>
+  </si>
+  <si>
+    <t>平均开放次数（年化）</t>
+  </si>
+  <si>
+    <t>开放期业务</t>
+  </si>
+  <si>
+    <t>开放期业务说明</t>
+  </si>
+  <si>
+    <t>资金托管账号</t>
+  </si>
+  <si>
+    <t>资金托管账户</t>
+  </si>
+  <si>
+    <t>产品类型</t>
+  </si>
+  <si>
+    <t>计息基础</t>
+  </si>
+  <si>
+    <t>受托职责</t>
+  </si>
+  <si>
+    <t>客户类型</t>
+  </si>
+  <si>
+    <t>是否母行划转产品</t>
+  </si>
+  <si>
+    <t>现金管理类产品-是否完全符合</t>
+  </si>
+  <si>
+    <t>是否养老理财</t>
+  </si>
+  <si>
+    <t>是否收益权转让产品</t>
+  </si>
+  <si>
+    <t>发行状态</t>
+  </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>操作类型</t>
-  </si>
-  <si>
-    <t>产品代码</t>
-  </si>
-  <si>
-    <t>产品类型</t>
-  </si>
-  <si>
-    <t>募集起始日期</t>
-  </si>
-  <si>
-    <t>募集结束日期</t>
-  </si>
-  <si>
-    <t>是否结构化分级产品</t>
-  </si>
-  <si>
-    <t>开放模式</t>
-  </si>
-  <si>
-    <t>规律开放周期</t>
-  </si>
-  <si>
-    <t>其他规律开放周期（天）</t>
-  </si>
-  <si>
-    <t>无规律开放说明</t>
-  </si>
-  <si>
-    <t>首次开放周期起始日</t>
-  </si>
-  <si>
-    <t>节假日是否开放</t>
-  </si>
-  <si>
-    <t>平均开放次数（年化）</t>
-  </si>
-  <si>
-    <t>开放期业务</t>
-  </si>
-  <si>
-    <t>开放期业务说明</t>
-  </si>
-  <si>
-    <t>受托职责</t>
-  </si>
-  <si>
-    <t>管理方式</t>
-  </si>
-  <si>
-    <t>客户类型</t>
-  </si>
-  <si>
-    <t>业绩比较基准说明</t>
-  </si>
-  <si>
-    <t>资金托管账号</t>
-  </si>
-  <si>
-    <t>资金托管账户</t>
-  </si>
-  <si>
-    <t>是否母行划转产品</t>
-  </si>
-  <si>
-    <t>现金管理类产品-是否完全符合</t>
+    <t>M 货币型产品</t>
   </si>
   <si>
     <t>N 净值型产品</t>
   </si>
   <si>
+    <t>R 利率型产品</t>
+  </si>
+  <si>
     <t>01 是</t>
   </si>
   <si>
@@ -106,92 +134,82 @@
     <t>01 有规律开放</t>
   </si>
   <si>
+    <t>02 无规律开放</t>
+  </si>
+  <si>
     <t>01 每天开放</t>
   </si>
   <si>
+    <t>02 每周开放一次</t>
+  </si>
+  <si>
+    <t>03 每两周开放一次</t>
+  </si>
+  <si>
+    <t>04 每月开放一次</t>
+  </si>
+  <si>
+    <t>05 每季度开放一次</t>
+  </si>
+  <si>
+    <t>06 每半年开放一次</t>
+  </si>
+  <si>
+    <t>07 每年开放一次</t>
+  </si>
+  <si>
+    <t>99 其他规律开放周期</t>
+  </si>
+  <si>
     <t>01 申赎皆可</t>
   </si>
   <si>
+    <t>02 仅可申购无限制</t>
+  </si>
+  <si>
+    <t>03 仅可赎回无限制</t>
+  </si>
+  <si>
+    <t>04 仅可申购有限制</t>
+  </si>
+  <si>
+    <t>05 仅可赎回有限制</t>
+  </si>
+  <si>
+    <t>99 其他</t>
+  </si>
+  <si>
     <t>01 主动管理</t>
   </si>
   <si>
-    <t>99 其他</t>
+    <t>02 被动管理</t>
+  </si>
+  <si>
+    <t>01 收益权转让</t>
   </si>
   <si>
     <t>01 集合管理</t>
   </si>
   <si>
+    <t>02 单独管理</t>
+  </si>
+  <si>
     <t>01 发行成功</t>
   </si>
   <si>
-    <t>02 单独管理</t>
-  </si>
-  <si>
     <t>02 发行失败</t>
   </si>
   <si>
     <t>03 确认发行</t>
   </si>
   <si>
-    <t>M 货币型产品</t>
-  </si>
-  <si>
-    <t>R 利率型产品</t>
-  </si>
-  <si>
-    <t>02 无规律开放</t>
-  </si>
-  <si>
-    <t>02 每周开放一次</t>
-  </si>
-  <si>
-    <t>03 每两周开放一次</t>
-  </si>
-  <si>
-    <t>04 每月开放一次</t>
-  </si>
-  <si>
-    <t>05 每季度开放一次</t>
-  </si>
-  <si>
-    <t>06 每半年开放一次</t>
-  </si>
-  <si>
-    <t>07 每年开放一次</t>
-  </si>
-  <si>
-    <t>99 其他规律开放周期</t>
-  </si>
-  <si>
-    <t>02 仅可申购无限制</t>
-  </si>
-  <si>
-    <t>03 仅可赎回无限制</t>
-  </si>
-  <si>
-    <t>04 仅可申购有限制</t>
-  </si>
-  <si>
-    <t>05 仅可赎回有限制</t>
-  </si>
-  <si>
-    <t>02 被动管理</t>
-  </si>
-  <si>
-    <t>01 收益权转让</t>
-  </si>
-  <si>
-    <t>发行机构代码</t>
-  </si>
-  <si>
-    <t>业绩比较基准上限%</t>
-  </si>
-  <si>
-    <t>业绩比较基准下限%</t>
-  </si>
-  <si>
-    <t>客户类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>1 单位</t>
+  </si>
+  <si>
+    <t>2 个人</t>
+  </si>
+  <si>
+    <t>3 单位及个人</t>
   </si>
   <si>
     <r>
@@ -200,7 +218,6 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>客户类型</t>
@@ -210,106 +227,214 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
-        <family val="2"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>填写规则：
 下边列表中的一个或多个，当选择多个时，用“,”隔开（注：英文的逗号）</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-单位,</t>
+  </si>
+  <si>
+    <t>2-个人,</t>
   </si>
   <si>
     <t>3-个人及单位,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2-个人,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1-单位,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否养老理财</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否收益权转让产品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计息基础</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发行状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 单位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2 个人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3 单位及个人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>到期日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>起息日</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,8 +447,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -333,23 +644,32 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom/>
@@ -357,29 +677,262 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF3F3F3F"/>
       </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -390,33 +943,77 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -465,7 +1062,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -500,7 +1097,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -674,401 +1271,364 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="13" bestFit="1" customWidth="1"/>
-    <col min="24" max="27" width="9" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="28.75" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9" customWidth="1"/>
+    <col min="3" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="19.25" customWidth="1"/>
+    <col min="10" max="11" width="18.375" customWidth="1"/>
+    <col min="12" max="12" width="17.25" customWidth="1"/>
+    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="23.5" customWidth="1"/>
+    <col min="16" max="16" width="15.125" customWidth="1"/>
+    <col min="17" max="17" width="19.25" customWidth="1"/>
+    <col min="18" max="18" width="15.125" customWidth="1"/>
+    <col min="19" max="19" width="21.375" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="15.125" customWidth="1"/>
+    <col min="22" max="23" width="13" customWidth="1"/>
+    <col min="24" max="27" width="9" customWidth="1"/>
+    <col min="28" max="28" width="17.25" customWidth="1"/>
+    <col min="29" max="29" width="28.75" customWidth="1"/>
+    <col min="30" max="30" width="13" customWidth="1"/>
+    <col min="31" max="31" width="19.25" customWidth="1"/>
+    <col min="32" max="32" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="31.35" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" ht="31.35" customHeight="1" spans="1:32">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
-        <v>53</v>
-      </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
-        <v>69</v>
-      </c>
       <c r="G1" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" t="s">
-        <v>13</v>
-      </c>
-      <c r="T1" t="s">
-        <v>14</v>
-      </c>
       <c r="U1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="V1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="Y1" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="Z1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AA1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AB1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AD1" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="AE1" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="AF1" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" ht="24.95" customHeight="1" spans="10:21">
       <c r="J2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="U2" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A2:A1048576">
       <formula1>"导出,新增,修改,删除"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="X2:X1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$2:$D$2</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="正确格式为1900-01-01" sqref="D2:D1048576 E2:E1048576 F2:F1048576 G2:G1048576 Q2:Q1048576">
+      <formula1>1</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H2:H1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$9:$B$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I2:I1048576 R2:R1048576 AB2:AE1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$3:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="M2:M1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$4:$B$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="N2:N1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$5:$H$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="T2:T1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$6:$F$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
       <formula1>"A/360,A/365"</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="正确格式为1900-01-01" sqref="D2:D1048576 E2:E1048576 F2:F1048576 G2:G1048576 Q2:Q1048576">
-      <formula1>1</formula1>
-      <formula2>2958465</formula2>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="Z2:Z1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$7:$B$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$11:$C$11</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="AF2:AF1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$10:$C$10</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_PRD_BASEINFO_ENUM!$A$9:$B$9</xm:f>
-          </x14:formula1>
-          <xm:sqref>H2:H1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_PRD_BASEINFO_ENUM!$A$10:$C$10</xm:f>
-          </x14:formula1>
-          <xm:sqref>AF2:AF1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_PRD_BASEINFO_ENUM!$A$2:$D$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>X2:X1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_PRD_BASEINFO_ENUM!$A$4:$B$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_PRD_BASEINFO_ENUM!$A$5:$H$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>N2:N1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_PRD_BASEINFO_ENUM!$A$6:$F$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>T2:T1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_PRD_BASEINFO_ENUM!$A$7:$B$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>Z2:Z1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_PRD_BASEINFO_ENUM!$A$3:$B$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>I2:I1048576 R2:R1048576 AB2:AE1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>CHB_PRD_BASEINFO_ENUM!$A$11:$C$11</xm:f>
-          </x14:formula1>
-          <xm:sqref>AA2:AA1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A2:H16"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="2" max="6" width="18.5" customWidth="1"/>
+    <col min="7" max="7" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" ht="24.95" customHeight="1" spans="1:3">
       <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" ht="24.95" customHeight="1" spans="1:2">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
         <v>37</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="4" ht="24.95" customHeight="1" spans="1:2">
+      <c r="A4" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" ht="24.95" customHeight="1" spans="1:8">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" ht="24.95" customHeight="1" spans="1:6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" ht="24.95" customHeight="1" spans="1:2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" ht="24.95" customHeight="1" spans="1:2">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" ht="24.95" customHeight="1" spans="1:2">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" ht="24.95" customHeight="1" spans="1:3">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="57.75" customHeight="1" spans="1:2">
+      <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:1">
+      <c r="A14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="57.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A15" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A16" s="4" t="s">
-        <v>58</v>
+    <row r="16" spans="1:1">
+      <c r="A16" s="6" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A13:B13"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbPrdBaseinfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbPrdBaseinfo.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
     <sheet name="CHB_PRD_BASEINFO_ENUM" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="74">
   <si>
     <t>操作类型</t>
   </si>
@@ -201,6 +202,22 @@
   </si>
   <si>
     <t>03 确认发行</t>
+  </si>
+  <si>
+    <t>01 ACT/366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 ACT/360
+</t>
+  </si>
+  <si>
+    <t>03 ACT/365</t>
+  </si>
+  <si>
+    <t>04 ACT/ACT</t>
+  </si>
+  <si>
+    <t>05 30/360</t>
   </si>
   <si>
     <t>1 单位</t>
@@ -248,20 +265,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="#\ ??/??"/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -277,65 +288,128 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,70 +425,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -449,61 +460,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -515,115 +634,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,21 +701,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -736,18 +732,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -757,6 +746,15 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -776,13 +774,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -791,165 +802,171 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
@@ -1402,7 +1419,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" ht="24.95" customHeight="1" spans="10:21">
+    <row r="2" ht="24" customHeight="1" spans="10:21">
       <c r="J2" t="s">
         <v>32</v>
       </c>
@@ -1418,47 +1435,93 @@
       <c r="P2" t="s">
         <v>32</v>
       </c>
+      <c r="Q2"/>
       <c r="U2" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A2:A1048576">
+  <dataValidations count="26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="AA2:AA1003">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$12:$C$12</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="Z2:Z1003">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$7:$B$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="Y2:Y1003">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$11:$E$11</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H1004:H1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$9:$B$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="A2:A1003">
       <formula1>"导出,新增,修改,删除"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="X2:X1048576">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$2:$D$2</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="正确格式为1900-01-01" sqref="D2:D1048576 E2:E1048576 F2:F1048576 G2:G1048576 Q2:Q1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="M2:M1003">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$4:$B$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A1004:A1048576">
+      <formula1>"导出,新增,修改,删除"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="正确格式为1900-01-01" sqref="D1004:D1048576 E1004:E1048576 F1004:F1048576 G1004:G1048576 Q1004:Q1048576">
       <formula1>1</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H2:H1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="正确格式为1900-01-01" sqref="D2:D1003 E2:E1003 F2:F1003 G2:G1003 Q2:Q1003">
+      <formula1>1</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="H2:H1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$9:$B$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I2:I1048576 R2:R1048576 AB2:AE1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="I2:I1003 R2:R1003 AB2:AB1003 AC2:AC1003 AD2:AD1003 AE2:AE1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$3:$B$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="M2:M1048576">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能输入整数！" sqref="O2:O1003">
+      <formula1>0</formula1>
+      <formula2>9999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I1004:I1048576 R1004:R1048576 AB1004:AE1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$3:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能输入数字!" sqref="J2:J1003 K2:K1003">
+      <formula1>-999999</formula1>
+      <formula2>999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="M1004:M1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$4:$B$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="N2:N1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="N2:N1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$5:$H$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="T2:T1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="X2:X1003">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$2:$D$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="N1004:N1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$5:$H$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="T2:T1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$6:$F$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="T1004:T1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$6:$F$6</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="X1004:X1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$2:$D$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1004:Y1048576">
       <formula1>"A/360,A/365"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="Z1004:Z1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$7:$B$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$11:$C$11</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="AF2:AF1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA1004:AA1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$12:$C$12</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="AF2:AF1003">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$10:$C$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="AF1004:AF1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$10:$C$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -1471,7 +1534,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:H16"/>
+  <dimension ref="A2:H17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -1587,7 +1650,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" ht="24.95" customHeight="1" spans="1:6">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -1597,38 +1660,67 @@
       <c r="C11" t="s">
         <v>64</v>
       </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" ht="57.75" customHeight="1" spans="1:2">
-      <c r="A13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="3"/>
+    <row r="14" ht="57.75" customHeight="1" spans="1:2">
+      <c r="A14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="5"/>
     </row>
-    <row r="14" ht="14.25" spans="1:1">
-      <c r="A14" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
-        <v>67</v>
+    <row r="15" ht="14.25" spans="1:1">
+      <c r="A15" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="6" t="s">
-        <v>68</v>
+      <c r="A16" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="8" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbPrdBaseinfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbPrdBaseinfo.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="产品基本信息" sheetId="1" r:id="rId1"/>
     <sheet name="CHB_PRD_BASEINFO_ENUM" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -265,12 +264,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="#\ ??/??"/>
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="#\ ??/??"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -288,6 +288,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -295,6 +309,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -302,56 +323,60 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -360,16 +385,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -383,56 +401,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -460,181 +460,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,6 +715,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -726,50 +735,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -797,164 +762,199 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -973,6 +973,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1419,7 +1422,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="10:21">
+    <row r="2" ht="24" customHeight="1" spans="4:21">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
       <c r="J2" t="s">
         <v>32</v>
       </c>
@@ -1435,7 +1442,7 @@
       <c r="P2" t="s">
         <v>32</v>
       </c>
-      <c r="Q2"/>
+      <c r="Q2" s="9"/>
       <c r="U2" t="s">
         <v>32</v>
       </c>
@@ -1471,35 +1478,38 @@
       <formula1>1</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1004:Y1048576">
+      <formula1>"A/360,A/365"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="H2:H1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$9:$B$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="I2:I1003 R2:R1003 AB2:AB1003 AC2:AC1003 AD2:AD1003 AE2:AE1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$3:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I1004:I1048576 R1004:R1048576 AB1004:AE1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$3:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能输入数字!" sqref="J2:J1003 K2:K1003 S2:S10 S11:S18 S19:S161 S162:S1025">
+      <formula1>-999999</formula1>
+      <formula2>999999</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="M1004:M1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$4:$B$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="N2:N1003">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$5:$H$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="X2:X1003">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$2:$D$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="N1004:N1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$5:$H$5</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能输入整数！" sqref="O2:O1003">
       <formula1>0</formula1>
       <formula2>9999999</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I1004:I1048576 R1004:R1048576 AB1004:AE1048576">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$3:$B$3</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能输入数字!" sqref="J2:J1003 K2:K1003">
-      <formula1>-999999</formula1>
-      <formula2>999999</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="M1004:M1048576">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$4:$B$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="N2:N1003">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$5:$H$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="X2:X1003">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$2:$D$2</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="N1004:N1048576">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$5:$H$5</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="T2:T1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$6:$F$6</formula1>
     </dataValidation>
@@ -1508,9 +1518,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="X1004:X1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$2:$D$2</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1004:Y1048576">
-      <formula1>"A/360,A/365"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="Z1004:Z1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$7:$B$7</formula1>
@@ -1712,15 +1719,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbPrdBaseinfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbPrdBaseinfo.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
   <si>
     <t>操作类型</t>
   </si>
@@ -201,22 +201,6 @@
   </si>
   <si>
     <t>03 确认发行</t>
-  </si>
-  <si>
-    <t>01 ACT/366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02 ACT/360
-</t>
-  </si>
-  <si>
-    <t>03 ACT/365</t>
-  </si>
-  <si>
-    <t>04 ACT/ACT</t>
-  </si>
-  <si>
-    <t>05 30/360</t>
   </si>
   <si>
     <t>1 单位</t>
@@ -264,13 +248,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="#\ ??/??"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -288,12 +271,57 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
@@ -302,44 +330,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -361,6 +368,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -369,68 +398,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -460,19 +443,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -484,19 +575,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -508,43 +605,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,91 +623,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,45 +684,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -750,15 +694,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -789,6 +724,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -797,164 +771,167 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -1423,10 +1400,10 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="4:21">
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
       <c r="J2" t="s">
         <v>32</v>
       </c>
@@ -1442,21 +1419,15 @@
       <c r="P2" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="9"/>
+      <c r="Q2" s="7"/>
       <c r="U2" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="26">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="AA2:AA1003">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$12:$C$12</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="Z2:Z1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$7:$B$7</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="Y2:Y1003">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$11:$E$11</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H1004:H1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$9:$B$9</formula1>
@@ -1478,9 +1449,6 @@
       <formula1>1</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1004:Y1048576">
-      <formula1>"A/360,A/365"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="H2:H1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$9:$B$9</formula1>
     </dataValidation>
@@ -1519,11 +1487,20 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="X1004:X1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$2:$D$2</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="Y2:Y1045">
+      <formula1>"A/360,A/365"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1046:Y1048576">
+      <formula1>"A/360,A/365"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="Z1004:Z1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$7:$B$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA1004:AA1048576">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$12:$C$12</formula1>
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$11:$C$11</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="AA2:AA1003">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$11:$C$11</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="AF2:AF1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$10:$C$10</formula1>
@@ -1541,7 +1518,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:H17"/>
+  <dimension ref="A2:H16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -1657,7 +1634,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" ht="24.95" customHeight="1" spans="1:6">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -1667,54 +1644,36 @@
       <c r="C11" t="s">
         <v>64</v>
       </c>
-      <c r="D11" t="s">
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" ht="57.75" customHeight="1" spans="1:2">
+      <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:1">
+      <c r="A14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" ht="57.75" customHeight="1" spans="1:2">
-      <c r="A14" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="5"/>
-    </row>
-    <row r="15" ht="14.25" spans="1:1">
-      <c r="A15" s="6" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="8" t="s">
-        <v>73</v>
+      <c r="A16" s="6" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbPrdBaseinfo.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbPrdBaseinfo.xlsx
@@ -249,11 +249,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -277,76 +277,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -360,6 +322,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -369,14 +338,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -390,32 +391,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -443,19 +443,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -467,37 +593,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -509,121 +611,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -684,6 +684,45 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -700,11 +739,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -724,21 +761,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -748,34 +770,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -785,148 +785,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1426,17 +1426,17 @@
     </row>
   </sheetData>
   <dataValidations count="26">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I1004:I1048576 R1004:R1048576 AB1004:AE1048576">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$3:$B$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="A2:A1003">
+      <formula1>"导出,新增,修改,删除"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="Z2:Z1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$7:$B$7</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H1004:H1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$9:$B$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="A2:A1003">
-      <formula1>"导出,新增,修改,删除"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="M2:M1003">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$4:$B$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A1004:A1048576">
       <formula1>"导出,新增,修改,删除"</formula1>
@@ -1455,13 +1455,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="I2:I1003 R2:R1003 AB2:AB1003 AC2:AC1003 AD2:AD1003 AE2:AE1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$3:$B$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="I1004:I1048576 R1004:R1048576 AB1004:AE1048576">
-      <formula1>CHB_PRD_BASEINFO_ENUM!$A$3:$B$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1046:Y1048576">
+      <formula1>"A/360,A/365"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能输入数字!" sqref="J2:J1003 K2:K1003 S2:S10 S11:S18 S19:S161 S162:S1025">
       <formula1>-999999</formula1>
       <formula2>999999</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="M2:M1003">
+      <formula1>CHB_PRD_BASEINFO_ENUM!$A$4:$B$4</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="M1004:M1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$4:$B$4</formula1>
     </dataValidation>
@@ -1481,17 +1484,14 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="T2:T1003">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$6:$F$6</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="Y2:Y1045">
+      <formula1>"A/360,A/365"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="T1004:T1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$6:$F$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="X1004:X1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$2:$D$2</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="温馨提示" error="该单元格只能选下拉框中的数据!" sqref="Y2:Y1045">
-      <formula1>"A/360,A/365"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1046:Y1048576">
-      <formula1>"A/360,A/365"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="Z1004:Z1048576">
       <formula1>CHB_PRD_BASEINFO_ENUM!$A$7:$B$7</formula1>
